--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1135,7 +1135,9 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-12" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>10-12 18:00</t>
+          <t>10-12 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>43.69</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -852,7 +856,7 @@
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.0242</t>
+          <t>2.0008</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 39.76</t>
+          <t>C+ 33.50</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1000,7 +1004,9 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -947,8 +947,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>27.78</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.97</t>

--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 14.20</t>
+          <t>C- 15.99</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -932,7 +932,11 @@
           <t>10-12 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>032690035.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>5+5</t>
@@ -941,7 +945,9 @@
       <c r="E4" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
@@ -985,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.50</t>
+          <t>C+ 30.47</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>8.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.20</t>
@@ -757,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 15.99</t>
+          <t>C- 15.31</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -780,7 +782,9 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.89</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -991,7 +995,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.47</t>
+          <t>B- 35.86</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-12.xlsx
+++ b/data/credit_bond_2026-10-12.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-16" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 35.86</t>
+          <t>B- 37.03</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
